--- a/karkard/output/کارکرد-شهریور-1405.xlsx
+++ b/karkard/output/کارکرد-شهریور-1405.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,43 +31,49 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="001F4E5F"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="B Nazanin"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="B Nazanin"/>
-      <color rgb="001F4E5F"/>
+      <color rgb="00404040"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
-      <sz val="12"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <color rgb="00595959"/>
-      <sz val="12"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="001F4E5F"/>
-      <sz val="13"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,37 +82,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
+        <fgColor rgb="00404040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF1FA"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00EAF4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,149 +121,149 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,7 +274,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -312,13 +313,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,13 +331,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +705,15 @@
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="95" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>بسمه تعالی</t>
@@ -727,7 +725,7 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>فرم ثبت شرح فعالیت روزانه نیروهای خرید خدمت مرکز فضای مجازی بسیج استان اصفهان</t>
@@ -739,7 +737,7 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>با احترام، بدینوسیله کارکرد برادر محسن ابوطالبیان در شهریور ماه ۱۴۰۵ بر اساس جدول ذیل حضورتان ارسال می‌گردد:</t>
@@ -751,7 +749,7 @@
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
     </row>
-    <row r="4" ht="6" customHeight="1">
+    <row r="4" ht="3" customHeight="1">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
@@ -759,7 +757,7 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
-    <row r="5" ht="50" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ایام ماه</t>
@@ -791,7 +789,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>۱</t>
@@ -823,7 +821,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>۲</t>
@@ -855,7 +853,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>۳</t>
@@ -887,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="25" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>۴</t>
@@ -919,7 +917,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="25" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>۵</t>
@@ -951,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>۶</t>
@@ -983,7 +981,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="25" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>۷</t>
@@ -1015,7 +1013,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>۸</t>
@@ -1035,7 +1033,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14" ht="25" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>۹</t>
@@ -1067,7 +1065,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1">
+    <row r="15" ht="25" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>۱۰</t>
@@ -1099,7 +1097,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16" ht="25" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>۱۱</t>
@@ -1131,7 +1129,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="25" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>۱۲</t>
@@ -1163,7 +1161,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>۱۳</t>
@@ -1195,7 +1193,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19" ht="25" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>۱۴</t>
@@ -1227,7 +1225,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1">
+    <row r="20" ht="25" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>۱۵</t>
@@ -1259,7 +1257,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="21" ht="25" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>۱۶</t>
@@ -1291,7 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22" ht="25" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>۱۷</t>
@@ -1323,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23" ht="25" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>۱۸</t>
@@ -1355,7 +1353,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
+    <row r="24" ht="25" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>۱۹</t>
@@ -1387,7 +1385,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="16" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
           <t>۲۰</t>
@@ -1407,7 +1405,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
+    <row r="26" ht="25" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>۲۱</t>
@@ -1439,7 +1437,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
+    <row r="27" ht="25" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>۲۲</t>
@@ -1471,7 +1469,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
+    <row r="28" ht="25" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>۲۳</t>
@@ -1503,7 +1501,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
+    <row r="29" ht="25" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>۲۴</t>
@@ -1535,7 +1533,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
+    <row r="30" ht="25" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>۲۵</t>
@@ -1567,7 +1565,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1">
+    <row r="31" ht="25" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>۲۶</t>
@@ -1599,7 +1597,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="16" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
           <t>۲۷</t>
@@ -1619,7 +1617,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
+    <row r="33" ht="25" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>۲۸</t>
@@ -1651,7 +1649,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>۲۹</t>
@@ -1683,7 +1681,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>۳۰</t>
@@ -1715,7 +1713,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="48" customHeight="1">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
           <t>۳۱</t>
@@ -1747,7 +1745,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
           <t>جمع ساعات کارکرد در ماه: ۲۰۴ ساعت و ۲۰ دقیقه</t>
@@ -1759,8 +1757,8 @@
       <c r="E37" s="23" t="n"/>
       <c r="F37" s="23" t="n"/>
     </row>
-    <row r="38" ht="10" customHeight="1"/>
-    <row r="39" ht="26" customHeight="1">
+    <row r="38" ht="4" customHeight="1"/>
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
           <t>امضاء فرد</t>
@@ -1780,21 +1778,21 @@
       </c>
       <c r="F39" s="24" t="n"/>
     </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="25" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1809,9 +1807,9 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0.35" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.18" right="0.18" top="0.2" bottom="0.2" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;9 کارکرد شهریور ۱۴۰۵ ـ صفحه &amp;P از &amp;N</oddFooter>

--- a/karkard/output/کارکرد-شهریور-1405.xlsx
+++ b/karkard/output/کارکرد-شهریور-1405.xlsx
@@ -802,12 +802,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۶:۳۰</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۹:۳۰</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>۱۵:۳۰</t>
+          <t>۱۷:۳۰</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۰۵</t>
+          <t>۰۹:۳۰</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۰۵</t>
+          <t>۱۷:۳۰</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ دریافت و دسته‌بندی گزارش‌های ماهانه نواحی برای تهیه کارنامه عملکرد؛ انتشار محتوای تولیدشده در کانال‌های ایتا، روبیکا و تلگرام استان؛ بررسی و تطبیق آمار فعالیت‌های ثبت‌شده نواحی با مستندات ارسالی</t>
+          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ دریافت و دسته‌بندی گزارش‌های ماهانه نواحی برای تهیه کارنامه عملکرد؛ انتشار محتوای تولیدشده در کانال‌های ایتا، روبیکا و تلگرام استان؛ بررسی و تطبیق آمار فعالیت‌های ثبت‌شده نواحی با مستندات ارسالی؛ تجمیع و تکمیل گزارش کارکرد ماه مرداد</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>۰۸:۰۵</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>۱۱:۲۵</t>
+          <t>۱۲:۲۰</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>۰۹:۵۰</t>
+          <t>۰۸:۵۰</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>۱۱:۱۰</t>
+          <t>۱۰:۱۰</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۳۵</t>
+          <t>۱۷:۲۰</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۴۰</t>
+          <t>۱۷:۳۰</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۹:۲۰</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۱۵</t>
+          <t>۱۸:۰۵</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۰۰</t>
+          <t>۰۸:۴۰</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۴۰</t>
+          <t>۰۸:۴۵</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۵۰</t>
+          <t>۱۲:۵۵</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>۱۰:۰۵</t>
+          <t>۰۹:۰۵</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>۱۱:۱۰</t>
+          <t>۱۰:۱۰</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۹:۳۰</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۵</t>
+          <t>۱۸:۲۵</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۴۰</t>
+          <t>۰۸:۴۰</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>۱۵:۴۵</t>
+          <t>۱۶:۴۵</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۰۵</t>
+          <t>۰۸:۱۰</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۱۰</t>
+          <t>۱۶:۱۵</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۴۰</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۷:۱۰</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۸:۲۵</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۱۵</t>
+          <t>۱۶:۱۵</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>۰۸:۰۵</t>
+          <t>۰۸:۵۵</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۲۵</t>
+          <t>۱۲:۱۵</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۵۰</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۲۵</t>
+          <t>۱۶:۴۰</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۹:۰۰</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>۱۵:۴۰</t>
+          <t>۱۷:۱۰</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۵۰</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۸:۰۵</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۴۰</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۳۰</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۴۰</t>
+          <t>۱۶:۰۵</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۱۰</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۲۰</t>
+          <t>۱۱:۴۵</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۴۰</t>
+          <t>۰۹:۲۰</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۵۵</t>
+          <t>۱۸:۳۵</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۹:۲۵</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۰۰</t>
+          <t>۱۸:۰۰</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۹:۰۰</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۲۵</t>
+          <t>۱۷:۰۰</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>۰۸:۰۰</t>
+          <t>۰۸:۴۰</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>۱۶:۴۵</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">

--- a/karkard/output/کارکرد-شهریور-1405.xlsx
+++ b/karkard/output/کارکرد-شهریور-1405.xlsx
@@ -1809,7 +1809,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.18" right="0.18" top="0.2" bottom="0.2" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;9 کارکرد شهریور ۱۴۰۵ ـ صفحه &amp;P از &amp;N</oddFooter>

--- a/karkard/output/کارکرد-شهریور-1405.xlsx
+++ b/karkard/output/کارکرد-شهریور-1405.xlsx
@@ -73,7 +73,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -102,11 +102,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
@@ -263,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -304,15 +299,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -331,7 +317,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,17 +793,17 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۳۰</t>
+          <t>۱۶:۳۵</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>۸:۱۰</t>
+          <t>۸:۱۵</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ جمع‌آوری گزارش کارکرد ماه گذشته از نواحی و بررسی اولیه؛ به‌روزرسانی بخش سنجاق‌شده کانال و انتشار اطلاعیه‌های جدید ناحیه شاهین شهر؛ رصد اخبار و جریانات فضای مجازی استان و تهیه خلاصه تحلیلی روزانه</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ جمع‌آوری گزارش کارکرد ماه گذشته از نواحی و بررسی اولیه؛ به‌روزرسانی بخش سنجاق‌شده کانال و انتشار اطلاعیه‌های جدید ناحیه نایین؛ رصد اخبار و جریانات فضای مجازی استان و تهیه خلاصه تحلیلی روزانه</t>
         </is>
       </c>
     </row>
@@ -849,7 +835,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری ارسال گزارش عملکرد ماه قبل از نواحی باقی‌مانده؛ بررسی کیفیت مستندات بارگذاری‌شده نواحی در سامانه‌ها و اعلام نواقص؛ هماهنگی با مسئول فضای مجازی ناحیه خوانسار برای برنامه‌ریزی اقدامات ماه آینده</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری ارسال گزارش عملکرد ماه قبل از نواحی باقی‌مانده؛ بررسی کیفیت مستندات بارگذاری‌شده نواحی در سامانه‌ها و اعلام نواقص؛ هماهنگی با مسئول فضای مجازی ناحیه نجف آباد برای برنامه‌ریزی اقدامات ماه آینده</t>
         </is>
       </c>
     </row>
@@ -871,12 +857,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۳۰</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>۸:۰۰</t>
+          <t>۸:۱۰</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -903,12 +889,12 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۲۵</t>
+          <t>۱۷:۴۵</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>۸:۵۵</t>
+          <t>۹:۱۵</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -960,24 +946,12 @@
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>۰۸:۵۰</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>۱۰:۱۰</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>۱:۲۰</t>
-        </is>
-      </c>
+      <c r="C11" s="15" t="inlineStr"/>
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی) ـ پاسخگویی تلفنی به نواحی و پیگیری امور ضروری کانال‌ها (دورکاری)</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۶ شهریور)</t>
         </is>
       </c>
     </row>
@@ -1014,22 +988,22 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>۸</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>یکشنبه</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr"/>
-      <c r="D13" s="18" t="inlineStr"/>
-      <c r="E13" s="18" t="inlineStr"/>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>تعطیل رسمی (میلاد رسول اکرم (ص) و امام جعفر صادق (ع))</t>
+      <c r="C13" s="15" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>تعطیل رسمی (میلاد رسول اکرم (ص) و امام جعفر صادق (ع)) ـ روز ۸ شهریور</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1035,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ بارگذاری و انتشار پوسترها و کلیپ‌های جدید در کانال‌های استانی؛ ارتباط با مسئول نسرا در ناحیه مبارکه و پیگیری روند اجرای برنامه‌های آموزشی</t>
+          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ بارگذاری و انتشار پوسترها و کلیپ‌های جدید در کانال‌های استانی؛ ارتباط با مسئول نسرا در ناحیه کوهپایه و پیگیری روند اجرای برنامه‌های آموزشی</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1067,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ طراحی قالب گرافیکی جدید برای پست‌های مناسبتی کانال؛ بررسی گزارش‌های ارسالی ناحیه شهرضا و رفع اشکال موارد ناقص</t>
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ طراحی قالب گرافیکی جدید برای پست‌های مناسبتی کانال؛ بررسی گزارش‌های ارسالی ناحیه شاهین شهر و رفع اشکال موارد ناقص</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1089,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۴۰</t>
+          <t>۱۷:۵۰</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>۹:۰۰</t>
+          <t>۹:۱۰</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -1147,12 +1121,12 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>۱۲:۵۵</t>
+          <t>۱۳:۰۰</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>۴:۱۰</t>
+          <t>۴:۱۵</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -1172,24 +1146,12 @@
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>۰۹:۰۵</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>۱۰:۱۰</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>۱:۰۵</t>
-        </is>
-      </c>
+      <c r="C18" s="15" t="inlineStr"/>
+      <c r="D18" s="15" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی (دورکاری)</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۱۳ شهریور)</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1205,17 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۴۵</t>
+          <t>۱۶:۵۵</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>۸:۰۵</t>
+          <t>۸:۱۵</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ هماهنگی برگزاری کارگاه آموزشی ویژه فعالان رسانه‌ای ناحیه فریدن؛ رصد عملکرد کانال‌های ناحیه نطنز و مقایسه با میانگین استانی</t>
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ هماهنگی برگزاری کارگاه آموزشی ویژه فعالان رسانه‌ای ناحیه شهرضا؛ رصد عملکرد کانال‌های ناحیه خوانسار و مقایسه با میانگین استانی</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1269,12 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۱۰</t>
+          <t>۱۷:۱۵</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>۸:۴۰</t>
+          <t>۸:۴۵</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -1339,17 +1301,17 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۱۵</t>
+          <t>۱۶:۲۰</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>۷:۵۰</t>
+          <t>۷:۵۵</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ انتشار گزارش تصویری از فعالیت‌های برتر نواحی در کانال استان؛ تولید محتوای آموزشی ویژه ناحیه فریدون شهر بر اساس نیاز اعلامی</t>
+          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ انتشار گزارش تصویری از فعالیت‌های برتر نواحی در کانال استان؛ تولید محتوای آموزشی ویژه ناحیه فریدن بر اساس نیاز اعلامی</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1333,12 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>۱۲:۱۵</t>
+          <t>۱۲:۴۰</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>۳:۲۰</t>
+          <t>۳:۴۵</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -1386,22 +1348,22 @@
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>۲۰</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr"/>
-      <c r="D25" s="18" t="inlineStr"/>
-      <c r="E25" s="18" t="inlineStr"/>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>جمعه (تعطیل هفتگی)</t>
+      <c r="C25" s="15" t="inlineStr"/>
+      <c r="D25" s="15" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr"/>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>جمعه (تعطیل هفتگی ـ روز ۲۰ شهریور)</t>
         </is>
       </c>
     </row>
@@ -1455,17 +1417,17 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۱۰</t>
+          <t>۱۷:۲۰</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>۸:۱۰</t>
+          <t>۸:۲۰</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری تشکیل و فعال‌سازی تیم تولید محتوای ناحیه ورزنه؛ پایش کانال‌های سواد رسانه‌ای نواحی و شناسایی نقاط قوت و ضعف</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری تشکیل و فعال‌سازی تیم تولید محتوای ناحیه فلاورجان؛ پایش کانال‌های سواد رسانه‌ای نواحی و شناسایی نقاط قوت و ضعف</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1459,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ رصد و پایش فعالیت‌های فضای مجازی ناحیه کاشان و ثبت گزارش روزانه؛ پیگیری به‌روزرسانی اطلاعات عوامل اجرایی نواحی در سامانه نسرا</t>
+          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ رصد و پایش فعالیت‌های فضای مجازی ناحیه دهاقان و ثبت گزارش روزانه؛ پیگیری به‌روزرسانی اطلاعات عوامل اجرایی نواحی در سامانه نسرا</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1481,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۲۵</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>۸:۴۵</t>
+          <t>۹:۰۰</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -1583,12 +1545,12 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۴۵</t>
+          <t>۱۱:۵۰</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>۳:۳۵</t>
+          <t>۳:۴۰</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -1598,22 +1560,22 @@
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>۲۷</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr"/>
-      <c r="D32" s="18" t="inlineStr"/>
-      <c r="E32" s="18" t="inlineStr"/>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>جمعه (تعطیل هفتگی)</t>
+      <c r="C32" s="15" t="inlineStr"/>
+      <c r="D32" s="15" t="inlineStr"/>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>جمعه (تعطیل هفتگی ـ روز ۲۷ شهریور)</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1607,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ پیگیری روند ثبت‌نام و برگزاری کلاس‌های سواد رسانه‌ای ناحیه خمینی شهر؛ تولید و ویرایش محتوای چندرسانه‌ای برای پویش‌های استانی</t>
+          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ پیگیری روند ثبت‌نام و برگزاری کلاس‌های سواد رسانه‌ای ناحیه تیران و کرون؛ تولید و ویرایش محتوای چندرسانه‌ای برای پویش‌های استانی</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1629,12 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>۱۸:۰۰</t>
+          <t>۱۸:۱۰</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>۸:۳۵</t>
+          <t>۸:۴۵</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -1709,74 +1671,74 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ بررسی نهایی مستندات ماه جاری و بستن پرونده گزارش ماهانه؛ تهیه بروشور آموزشی سواد رسانه‌ای ویژه مربیان ناحیه تیران و کرون؛ طراحی بنر اطلاع‌رسانی ویژه برنامه‌های هفته سواد رسانه‌ای</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ بررسی نهایی مستندات ماه جاری و بستن پرونده گزارش ماهانه؛ تهیه بروشور آموزشی سواد رسانه‌ای ویژه مربیان ناحیه مبارکه؛ طراحی بنر اطلاع‌رسانی ویژه برنامه‌های هفته سواد رسانه‌ای</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>۳۱</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>سه‌شنبه</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>۰۸:۴۰</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>۱۷:۲۵</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>۸:۴۵</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>۱۷:۳۵</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>۸:۵۵</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ تهیه گزارش تحلیلی عملکرد ماه و ثبت در پرونده ماهانه؛ هماهنگی با فعالان رسانه‌ای ناحیه درچه برای توسعه تیم تولید محتوا؛ رصد صفحات و کانال‌های منتسب به نواحی در پیام‌رسان‌های داخلی</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>جمع ساعات کارکرد در ماه: ۲۰۴ ساعت و ۲۰ دقیقه</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="20" t="n"/>
     </row>
     <row r="38" ht="4" customHeight="1"/>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>امضاء فرد</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>امضاء مسئول مرکز فضای مجازی</t>
         </is>
       </c>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>تأیید مرکز فضای مجازی بسیج استان</t>
         </is>
       </c>
-      <c r="F39" s="24" t="n"/>
+      <c r="F39" s="21" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="n"/>
